--- a/data/trans_orig/IP19_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP19_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22219</t>
+          <t>22858</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36503</t>
+          <t>36732</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14836</t>
+          <t>14719</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27517</t>
+          <t>27932</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41139</t>
+          <t>41791</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59966</t>
+          <t>60616</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54364</t>
+          <t>54135</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68648</t>
+          <t>68009</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59328</t>
+          <t>58913</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72009</t>
+          <t>72126</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117746</t>
+          <t>117096</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>136573</t>
+          <t>135921</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,48%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>126341</t>
+          <t>127447</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>157987</t>
+          <t>158954</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>131739</t>
+          <t>131405</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>164489</t>
+          <t>163624</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>268324</t>
+          <t>268956</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>312012</t>
+          <t>313210</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,1%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>257410</t>
+          <t>256443</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>289056</t>
+          <t>287950</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>312502</t>
+          <t>313367</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>345252</t>
+          <t>345586</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>580376</t>
+          <t>579178</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>624064</t>
+          <t>623432</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,86%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41461</t>
+          <t>40841</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60606</t>
+          <t>60834</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34048</t>
+          <t>33485</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52079</t>
+          <t>51353</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>79183</t>
+          <t>80082</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105511</t>
+          <t>105710</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,82%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113460</t>
+          <t>113232</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>132605</t>
+          <t>133225</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>106059</t>
+          <t>106785</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>124090</t>
+          <t>124653</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>226694</t>
+          <t>226495</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>253022</t>
+          <t>252123</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>75,89%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>200664</t>
+          <t>200706</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>240991</t>
+          <t>241117</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>192041</t>
+          <t>191403</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>232289</t>
+          <t>231240</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>407536</t>
+          <t>405300</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>463546</t>
+          <t>463751</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,07%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>439339</t>
+          <t>439213</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>479666</t>
+          <t>479624</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>489685</t>
+          <t>490734</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>529933</t>
+          <t>530571</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>938758</t>
+          <t>938553</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>994768</t>
+          <t>997004</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,1%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18877</t>
+          <t>19017</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32554</t>
+          <t>33023</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22271</t>
+          <t>22516</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37069</t>
+          <t>37882</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44476</t>
+          <t>44695</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64435</t>
+          <t>64876</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59815</t>
+          <t>59346</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73492</t>
+          <t>73352</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49123</t>
+          <t>48310</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63921</t>
+          <t>63676</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>114126</t>
+          <t>113685</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>134085</t>
+          <t>133866</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,97%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>122051</t>
+          <t>122415</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>154902</t>
+          <t>153118</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>118506</t>
+          <t>117805</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>152260</t>
+          <t>151997</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>247983</t>
+          <t>249210</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>292754</t>
+          <t>294788</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,23%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>297308</t>
+          <t>299092</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>330159</t>
+          <t>329795</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>339441</t>
+          <t>339704</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>373195</t>
+          <t>373896</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>651157</t>
+          <t>649123</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>695928</t>
+          <t>694701</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,6%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47647</t>
+          <t>48289</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68181</t>
+          <t>69689</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44037</t>
+          <t>43918</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64105</t>
+          <t>64081</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97928</t>
+          <t>96791</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125419</t>
+          <t>124995</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,02%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98631</t>
+          <t>97123</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>119165</t>
+          <t>118523</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>106760</t>
+          <t>106784</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>126828</t>
+          <t>126947</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>212259</t>
+          <t>212683</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>239750</t>
+          <t>240887</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>71,34%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>199907</t>
+          <t>198122</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>239439</t>
+          <t>237449</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>196871</t>
+          <t>199123</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>237849</t>
+          <t>237831</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>407588</t>
+          <t>407267</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>464717</t>
+          <t>467038</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,99%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>471952</t>
+          <t>473942</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>511484</t>
+          <t>513269</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>510910</t>
+          <t>510928</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>551888</t>
+          <t>549636</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>995433</t>
+          <t>993112</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1052562</t>
+          <t>1052883</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>72,11%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>6704</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16876</t>
+          <t>15947</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7841</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19013</t>
+          <t>18848</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17379</t>
+          <t>17276</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31594</t>
+          <t>30922</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,16%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42502</t>
+          <t>43431</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52380</t>
+          <t>52674</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49601</t>
+          <t>49766</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60773</t>
+          <t>60351</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>96399</t>
+          <t>97071</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110614</t>
+          <t>110717</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,5%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>128200</t>
+          <t>130353</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>161603</t>
+          <t>162817</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>122639</t>
+          <t>122292</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>158125</t>
+          <t>155851</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>263575</t>
+          <t>262413</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>309308</t>
+          <t>308717</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>310687</t>
+          <t>309473</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>344090</t>
+          <t>341937</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>330610</t>
+          <t>332884</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>366096</t>
+          <t>366443</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>651717</t>
+          <t>652308</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>697450</t>
+          <t>698612</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,69%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47099</t>
+          <t>46160</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66848</t>
+          <t>66682</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48204</t>
+          <t>49951</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70064</t>
+          <t>71289</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>101820</t>
+          <t>98955</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130946</t>
+          <t>129862</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,05%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>105855</t>
+          <t>106021</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>125604</t>
+          <t>126543</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117431</t>
+          <t>116206</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>139291</t>
+          <t>137544</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>229251</t>
+          <t>230335</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>258377</t>
+          <t>261242</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>72,53%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>193627</t>
+          <t>192453</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>234321</t>
+          <t>231535</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>191404</t>
+          <t>189228</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>233289</t>
+          <t>230300</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>394224</t>
+          <t>396190</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>455617</t>
+          <t>453203</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>470050</t>
+          <t>472836</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>510744</t>
+          <t>511918</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>511555</t>
+          <t>514544</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>553440</t>
+          <t>555616</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>993598</t>
+          <t>996012</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1054991</t>
+          <t>1053025</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,66%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10623</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12731</t>
+          <t>12753</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7550</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19392</t>
+          <t>19776</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43092</t>
+          <t>42741</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51106</t>
+          <t>51035</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47209</t>
+          <t>47187</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56648</t>
+          <t>56511</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94262</t>
+          <t>93878</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>106104</t>
+          <t>105627</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>92,94%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>101759</t>
+          <t>97510</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143614</t>
+          <t>143593</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136112</t>
+          <t>135335</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>190940</t>
+          <t>186816</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>247996</t>
+          <t>247828</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>316961</t>
+          <t>317651</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>309521</t>
+          <t>309542</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>351376</t>
+          <t>355625</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>321227</t>
+          <t>325351</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>376055</t>
+          <t>376832</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>648341</t>
+          <t>647651</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>717306</t>
+          <t>717474</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,33%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48784</t>
+          <t>47548</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68884</t>
+          <t>67357</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59842</t>
+          <t>59207</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84695</t>
+          <t>83208</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114027</t>
+          <t>114256</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>145394</t>
+          <t>145326</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,5%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79442</t>
+          <t>80969</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>99542</t>
+          <t>100778</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93569</t>
+          <t>95056</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>118422</t>
+          <t>119057</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>181196</t>
+          <t>181264</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>212563</t>
+          <t>212334</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>65,02%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>162474</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>211914</t>
+          <t>212413</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>210840</t>
+          <t>210294</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>268717</t>
+          <t>266762</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>384559</t>
+          <t>384336</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>459488</t>
+          <t>461143</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>443261</t>
+          <t>442762</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>492701</t>
+          <t>495075</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>481654</t>
+          <t>483609</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>539531</t>
+          <t>540077</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>946058</t>
+          <t>944403</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1020987</t>
+          <t>1021210</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,66%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP19_R-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20706</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14869</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>27084</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>23,84%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>17,12%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>31,19%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>29407</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>22858</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>36732</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>22421</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>36606</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>32,36%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>25,16%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>40,42%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>20706</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>14719</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>27932</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>23,84%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41791</t>
+          <t>40589</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60616</t>
+          <t>60117</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,83%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>66139</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>59761</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>71976</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>76,16%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>68,81%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>82,88%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>61460</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>54135</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>68009</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>54261</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>68446</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>67,64%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>59,58%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>74,84%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>66139</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>58913</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>72126</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>76,16%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117096</t>
+          <t>117595</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>135921</t>
+          <t>137123</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>77,16%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>148077</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>131836</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>166981</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>31,04%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>27,64%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>35,01%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>141882</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>127447</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>158954</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>126450</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>156955</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>34,16%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>30,68%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>38,27%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>148077</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>131405</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>163624</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>31,04%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>268956</t>
+          <t>268002</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>313210</t>
+          <t>313316</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,11%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>328914</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>310010</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>345155</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>68,96%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>64,99%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>72,36%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>418</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>273515</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>256443</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>287950</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>258442</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>288947</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>65,84%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>61,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>69,32%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>496</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>328914</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>313367</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>345586</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>68,96%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>579178</t>
+          <t>579072</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>623432</t>
+          <t>624386</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,97%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>415397</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>415397</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>415397</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>42541</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>34026</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>51976</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>26,9%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>21,52%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>32,87%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>50023</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>40841</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>60834</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>40605</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>60176</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>28,74%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>23,46%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>34,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>42541</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>33485</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>51353</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>26,9%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>80082</t>
+          <t>79801</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105710</t>
+          <t>106455</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,04%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>115597</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>106162</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>124112</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>73,1%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>67,13%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>78,48%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>124043</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>113232</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>133225</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>113890</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>133461</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>71,26%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>65,05%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>76,54%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>115597</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>106785</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>124653</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>73,1%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>226495</t>
+          <t>225750</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>252123</t>
+          <t>252404</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,98%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>211324</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>191882</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>231416</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>29,27%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>26,58%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>32,05%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>325</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>221311</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>200706</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>241117</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>203349</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>241462</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>32,53%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>29,5%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>35,44%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>211324</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>191403</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>231240</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>29,27%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>405300</t>
+          <t>405660</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>463751</t>
+          <t>459488</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,77%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>510650</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>490558</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>530092</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>70,73%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>67,95%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>73,42%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>692</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>459019</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>439213</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>479624</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>438868</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>476981</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>67,47%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>64,56%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>70,5%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>768</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>510650</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>490734</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>530571</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>70,73%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>938553</t>
+          <t>942816</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>997004</t>
+          <t>996644</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,07%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1017</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>680330</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>680330</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>680330</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>29162</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22895</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>37678</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>33,83%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>26,56%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>43,71%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>24962</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19017</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>33023</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>18740</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>32413</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>27,02%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20,59%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>35,75%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>29162</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>22516</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>37882</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>33,83%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44695</t>
+          <t>44841</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64876</t>
+          <t>64961</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,38%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>57030</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>48514</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>63297</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>66,17%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>56,29%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>73,44%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>67407</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>59346</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>73352</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>59956</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>73629</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>72,98%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>64,25%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>79,41%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>57030</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>48310</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>63676</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>66,17%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113685</t>
+          <t>113600</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>133866</t>
+          <t>133720</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,89%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>134519</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>119574</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>151057</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>27,36%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>24,32%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>30,72%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>136686</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>122415</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>153118</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>120522</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>152848</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>30,23%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>27,07%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>33,86%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>134519</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>117805</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>151997</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>27,36%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>249210</t>
+          <t>249596</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>294788</t>
+          <t>296167</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,38%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>357182</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>340644</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>372127</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>72,64%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>69,28%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>75,68%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>459</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>315524</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>299092</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>329795</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>299362</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>331688</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>69,77%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>66,14%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>72,93%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>513</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>357182</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>339704</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>373896</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>72,64%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>649123</t>
+          <t>647744</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>694701</t>
+          <t>694315</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,56%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>491701</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>491701</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>491701</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>655</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>452210</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>452210</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>452210</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>704</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>491701</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>491701</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>491701</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>53722</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>44343</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>64456</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>31,44%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>25,95%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>37,72%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>57398</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>48289</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>69689</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>47680</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>67959</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>34,41%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>28,95%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>41,78%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>53722</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>43918</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>64081</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>31,44%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96791</t>
+          <t>98363</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>124995</t>
+          <t>126205</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,37%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>117143</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>106409</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>126522</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>68,56%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>62,28%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>74,05%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>109414</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>97123</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>118523</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>98853</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>119132</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>65,59%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>58,22%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>71,05%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>117143</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>106784</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>126947</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>68,56%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>212683</t>
+          <t>211473</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>240887</t>
+          <t>239315</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>70,87%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>170865</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>170865</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>170865</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>170865</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>170865</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>170865</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>217403</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>197188</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>238656</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>29,04%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>26,34%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>31,87%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>314</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>219046</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>198122</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>237449</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>198759</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>239621</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>30,79%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>27,85%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>33,38%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>217403</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>199123</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>237831</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>29,04%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>407267</t>
+          <t>405912</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>467038</t>
+          <t>465326</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,87%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>531356</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>510103</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>551571</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>70,96%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>68,13%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>73,66%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>711</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>492345</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>473942</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>513269</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>471770</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>512632</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>69,21%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>66,62%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>72,15%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>759</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>531356</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>510928</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>549636</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>70,96%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>993112</t>
+          <t>994824</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1052883</t>
+          <t>1054238</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,2%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1067</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>748759</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>748759</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>748759</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1025</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>711391</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1067</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>748759</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>748759</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>748759</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12609</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8008</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18972</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>18,38%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11,67%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>27,65%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>11072</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6704</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15947</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6870</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>16837</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>18,65%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,29%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>26,86%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12609</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8263</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>18848</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>18,38%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>17520</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30922</t>
+          <t>32088</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>56005</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>49642</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>60606</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>81,62%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>72,35%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>88,33%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>48306</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>43431</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>52674</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>42541</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>52508</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>81,35%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>73,14%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>88,71%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>56005</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>49766</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>60351</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>81,62%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97071</t>
+          <t>95905</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110717</t>
+          <t>110473</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,31%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>138876</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>123356</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>155940</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>28,42%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>25,24%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>31,91%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>146367</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>130353</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>162817</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>129609</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>164213</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>30,99%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>27,6%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>34,47%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>138876</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>122292</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>155851</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>28,42%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>262413</t>
+          <t>261198</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>308717</t>
+          <t>309136</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,17%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>349859</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>332795</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>365379</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>71,58%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>68,09%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>74,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>499</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>325923</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>309473</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>341937</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>308077</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>342681</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>69,01%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>65,53%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>72,4%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>349859</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>332884</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>366443</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>71,58%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>652308</t>
+          <t>651889</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>698612</t>
+          <t>699827</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>72,82%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>59228</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>48714</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>69880</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>31,59%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>25,98%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>37,27%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>55857</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>46160</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>66682</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>46094</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>65479</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>32,34%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>26,73%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>38,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>59228</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>49951</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>71289</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>31,59%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98955</t>
+          <t>101460</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>129862</t>
+          <t>129741</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,02%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>128267</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>117615</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>138781</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>68,41%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>62,73%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>74,02%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>116846</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>106021</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>126543</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>107224</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>126609</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>67,66%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>61,39%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>73,27%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>128267</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>116206</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>137544</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>68,41%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>230335</t>
+          <t>230456</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>261242</t>
+          <t>258737</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>71,83%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>210713</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>191031</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>232014</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>28,29%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>25,65%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>31,15%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>213296</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>192453</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>231535</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>192744</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>232144</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>30,28%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>27,32%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>32,87%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>210713</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>189228</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>230300</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>28,29%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>396190</t>
+          <t>394078</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>453203</t>
+          <t>450867</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>774</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>534131</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>512830</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>553813</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>71,71%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>68,85%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>74,35%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>750</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>491075</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>472836</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>511918</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>472227</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>511627</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>69,72%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>67,13%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>72,68%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>774</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>534131</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>514544</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>555616</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>71,71%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>996012</t>
+          <t>998348</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1053025</t>
+          <t>1055137</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,81%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6329</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2977</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11749</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,55%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>21,44%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5939</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2680</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10974</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,06%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,99%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12753</t>
+          <t>10826</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12910</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19776</t>
+          <t>19787</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>48477</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>43057</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>51829</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,45%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>78,56%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,57%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>47776</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>42741</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>51035</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>88,94%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>79,57%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,01%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52969</t>
+          <t>39383</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47187</t>
+          <t>34713</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56511</t>
+          <t>42437</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>100744</t>
+          <t>87861</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>93878</t>
+          <t>80558</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105627</t>
+          <t>92559</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,24%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>54806</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>54806</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>54806</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53715</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53715</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53715</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>59940</t>
+          <t>45539</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59940</t>
+          <t>45539</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59940</t>
+          <t>45539</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>113654</t>
+          <t>100345</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>113654</t>
+          <t>100345</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>113654</t>
+          <t>100345</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>146289</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>125819</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>171945</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>31,03%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>26,69%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>36,47%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>125373</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>97510</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>143593</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>27,67%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>21,52%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>31,69%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>156972</t>
+          <t>127652</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>135335</t>
+          <t>111888</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>186816</t>
+          <t>144087</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>282345</t>
+          <t>273942</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>247828</t>
+          <t>248909</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>317651</t>
+          <t>302800</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,77%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>325129</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>299473</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>345599</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>68,97%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>63,53%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>73,31%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>458</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>327762</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>309542</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>355625</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>72,33%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>68,31%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>78,48%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>477</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>355195</t>
+          <t>297564</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>325351</t>
+          <t>281129</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>376832</t>
+          <t>313328</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>682957</t>
+          <t>622692</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>647651</t>
+          <t>593834</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>717474</t>
+          <t>647725</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>72,24%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>471418</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>471418</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>471418</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>633</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>453135</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>453135</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>453135</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512167</t>
+          <t>425216</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512167</t>
+          <t>425216</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512167</t>
+          <t>425216</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>965302</t>
+          <t>896634</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>965302</t>
+          <t>896634</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>965302</t>
+          <t>896634</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>67882</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>57062</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>79741</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>41,62%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>34,98%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>48,89%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>57901</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>47548</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>67357</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>39,04%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>32,06%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>45,41%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>71501</t>
+          <t>59617</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59207</t>
+          <t>49737</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83208</t>
+          <t>69705</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>129402</t>
+          <t>127499</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114256</t>
+          <t>112380</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>145326</t>
+          <t>142541</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>45,7%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>95228</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>83369</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>106048</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>58,38%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>51,11%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>65,02%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>90425</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>80969</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>100778</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>60,96%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>54,59%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>67,94%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>106763</t>
+          <t>89151</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95056</t>
+          <t>79063</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>119057</t>
+          <t>99031</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>197188</t>
+          <t>184379</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>181264</t>
+          <t>169337</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>212334</t>
+          <t>199498</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>63,97%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>163110</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>163110</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>163110</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>148326</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>148326</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>148326</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>178264</t>
+          <t>148768</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>178264</t>
+          <t>148768</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>178264</t>
+          <t>148768</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>326590</t>
+          <t>311878</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>326590</t>
+          <t>311878</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>326590</t>
+          <t>311878</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>220500</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>194283</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>245630</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>31,99%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>28,18%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>35,63%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>189213</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>160100</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>212413</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>28,88%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>24,44%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>32,42%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>235444</t>
+          <t>193425</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>210294</t>
+          <t>173608</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>266762</t>
+          <t>213379</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>424657</t>
+          <t>413924</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>384336</t>
+          <t>383023</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>461143</t>
+          <t>448051</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>468834</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>443704</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>495051</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>68,01%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>64,37%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>71,82%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>660</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>465962</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>442762</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>495075</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>71,12%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>67,58%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>75,56%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>514927</t>
+          <t>426098</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>483609</t>
+          <t>406144</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>540077</t>
+          <t>445915</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>980889</t>
+          <t>894932</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>944403</t>
+          <t>860805</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1021210</t>
+          <t>925833</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>70,74%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>963</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>689334</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>689334</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>689334</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>928</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>655175</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>655175</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>655175</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>963</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>750371</t>
+          <t>619523</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>750371</t>
+          <t>619523</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>750371</t>
+          <t>619523</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1405546</t>
+          <t>1308856</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1405546</t>
+          <t>1308856</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1405546</t>
+          <t>1308856</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
